--- a/site/exports/bit-frontier-interdisciplinary-institute.xlsx
+++ b/site/exports/bit-frontier-interdisciplinary-institute.xlsx
@@ -453,7 +453,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="26.6" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
@@ -482,7 +482,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>核对日期</t>
+          <t>已记录来源检索日期</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -549,12 +549,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录；部分公开职业事实，教育、师承和人事在岗仍有缺项；抽样入口：物理学院·光学物理系ALL名录；本人任职正文：前沿交叉科学研究院。未核物理学院任职或双聘。现职称两官方页冲突，待核。</t>
+          <t>分批核实资料，不是完整名录；部分公开职业事实，教育、师承和人事在岗仍有缺项；抽样入口：物理学院·光学物理系ALL名录；本人任职正文：前沿交叉科学研究院。未核物理学院任职或双聘。现职称两官方页冲突，待核。；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
